--- a/data/trans_orig/P0901-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>59390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95172</t>
+          <t>95654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420942</t>
+          <t>422329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446131</t>
+          <t>446651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>254617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277613</t>
+          <t>277419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685285</t>
+          <t>684803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>718536</t>
+          <t>721067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>48877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>72837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336536</t>
+          <t>337491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354895</t>
+          <t>355068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323420</t>
+          <t>322988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345601</t>
+          <t>345943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665488</t>
+          <t>665962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>696491</t>
+          <t>696044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66495</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48228</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73315</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475894</t>
+          <t>475209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501744</t>
+          <t>500787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119554</t>
+          <t>117936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141432</t>
+          <t>140409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>601264</t>
+          <t>602529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636856</t>
+          <t>636589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115227</t>
+          <t>116324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157405</t>
+          <t>157429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87033</t>
+          <t>86210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123750</t>
+          <t>125120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212424</t>
+          <t>212398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269332</t>
+          <t>270691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080929</t>
+          <t>1080905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1123107</t>
+          <t>1122010</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590535</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627252</t>
+          <t>628075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1683288</t>
+          <t>1681929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1740196</t>
+          <t>1740222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53385</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74446</t>
+          <t>71957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108945</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106813</t>
+          <t>108885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148190</t>
+          <t>150848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297170</t>
+          <t>296464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320882</t>
+          <t>320873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459807</t>
+          <t>460774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494306</t>
+          <t>496795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>771117</t>
+          <t>768459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812494</t>
+          <t>810422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>215082</t>
+          <t>216257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275002</t>
+          <t>270455</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225000</t>
+          <t>226914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281828</t>
+          <t>285371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293450</t>
+          <t>293620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>973758</t>
+          <t>978305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1033678</t>
+          <t>1032503</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1265132</t>
+          <t>1261589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1321960</t>
+          <t>1320046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267777</t>
+          <t>264980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>334307</t>
+          <t>331447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>506665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>595016</t>
+          <t>597116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>793613</t>
+          <t>799583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>897589</t>
+          <t>903060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2935883</t>
+          <t>2938743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3002413</t>
+          <t>3005210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2783108</t>
+          <t>2781008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2867379</t>
+          <t>2871459</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5750725</t>
+          <t>5745254</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5854701</t>
+          <t>5848731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>50810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83418</t>
+          <t>79210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397920</t>
+          <t>399893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419537</t>
+          <t>419715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263994</t>
+          <t>263644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287677</t>
+          <t>288682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668247</t>
+          <t>672455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>700887</t>
+          <t>702795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>28285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56025</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71212</t>
+          <t>72244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>110297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353548</t>
+          <t>353008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381003</t>
+          <t>382253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281986</t>
+          <t>284211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308926</t>
+          <t>309726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647394</t>
+          <t>646511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>685596</t>
+          <t>684564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71537</t>
+          <t>71449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110445</t>
+          <t>109957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69010</t>
+          <t>69270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121012</t>
+          <t>119799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>166488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518970</t>
+          <t>519458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557878</t>
+          <t>557966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191119</t>
+          <t>190859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218555</t>
+          <t>217762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>719241</t>
+          <t>723056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>768532</t>
+          <t>769745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138257</t>
+          <t>139587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188321</t>
+          <t>191402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>98270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140286</t>
+          <t>141173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>250639</t>
+          <t>253755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315913</t>
+          <t>316220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970688</t>
+          <t>967607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1020752</t>
+          <t>1019422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626371</t>
+          <t>625484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666400</t>
+          <t>668387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1609754</t>
+          <t>1609447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1675028</t>
+          <t>1671912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55385</t>
+          <t>55100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85584</t>
+          <t>87454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187307</t>
+          <t>188013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239451</t>
+          <t>239254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254251</t>
+          <t>256195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313998</t>
+          <t>315715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425012</t>
+          <t>423142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455211</t>
+          <t>455496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522071</t>
+          <t>522268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>574215</t>
+          <t>573509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>958120</t>
+          <t>956403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017867</t>
+          <t>1015923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>22709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245267</t>
+          <t>248216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304729</t>
+          <t>304685</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>254273</t>
+          <t>257429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>316961</t>
+          <t>317623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245312</t>
+          <t>244173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259844</t>
+          <t>259439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>804622</t>
+          <t>804666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>864084</t>
+          <t>861135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1059272</t>
+          <t>1058610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1121960</t>
+          <t>1118804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>375517</t>
+          <t>371585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>455038</t>
+          <t>453750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689783</t>
+          <t>692183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>788054</t>
+          <t>794443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1083315</t>
+          <t>1086931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1216770</t>
+          <t>1208969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2966872</t>
+          <t>2968160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3046393</t>
+          <t>3050325</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2762071</t>
+          <t>2755682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2860342</t>
+          <t>2857942</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5755265</t>
+          <t>5763066</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5888720</t>
+          <t>5885104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57013</t>
+          <t>55477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30375</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>66713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104188</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372079</t>
+          <t>373615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399081</t>
+          <t>399364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289690</t>
+          <t>288757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316680</t>
+          <t>315830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671959</t>
+          <t>672720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707902</t>
+          <t>709434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57730</t>
+          <t>56275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51732</t>
+          <t>51706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85147</t>
+          <t>84444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339573</t>
+          <t>340317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359825</t>
+          <t>359332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314543</t>
+          <t>315998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341601</t>
+          <t>341139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664353</t>
+          <t>665056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697768</t>
+          <t>697794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>40309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>74637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110135</t>
+          <t>111198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454307</t>
+          <t>453776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481274</t>
+          <t>481605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117002</t>
+          <t>117924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139316</t>
+          <t>140095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577901</t>
+          <t>576838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613897</t>
+          <t>613399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114866</t>
+          <t>113202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157360</t>
+          <t>160396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>103466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145809</t>
+          <t>146541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228112</t>
+          <t>229405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290436</t>
+          <t>290066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>992278</t>
+          <t>989242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1034772</t>
+          <t>1036436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680067</t>
+          <t>679335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721003</t>
+          <t>722410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1685078</t>
+          <t>1685448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1747402</t>
+          <t>1746109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75128</t>
+          <t>73311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>108129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160443</t>
+          <t>157712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207545</t>
+          <t>207174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241744</t>
+          <t>246590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304084</t>
+          <t>306300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509568</t>
+          <t>512577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545578</t>
+          <t>547395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530699</t>
+          <t>531070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>577801</t>
+          <t>580532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1054866</t>
+          <t>1052650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117206</t>
+          <t>1112360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227550</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>289806</t>
+          <t>287449</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>235564</t>
+          <t>234457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>298132</t>
+          <t>295232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>269079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283694</t>
+          <t>283500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>792219</t>
+          <t>794576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>854475</t>
+          <t>856047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1071038</t>
+          <t>1073938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1133606</t>
+          <t>1134713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>323244</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>393483</t>
+          <t>390451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>636917</t>
+          <t>639379</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>734214</t>
+          <t>737408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>979603</t>
+          <t>976425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1107599</t>
+          <t>1102140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2992239</t>
+          <t>2995271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3062478</t>
+          <t>3067971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2797382</t>
+          <t>2794188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2894679</t>
+          <t>2892217</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5809719</t>
+          <t>5815178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5937715</t>
+          <t>5940893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>69954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83693</t>
+          <t>85287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117569</t>
+          <t>120012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449578</t>
+          <t>449189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>474054</t>
+          <t>474190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377002</t>
+          <t>377513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401912</t>
+          <t>400573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>835110</t>
+          <t>832667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>868986</t>
+          <t>867392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62530</t>
+          <t>60228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65537</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86039</t>
+          <t>87050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119681</t>
+          <t>120467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389683</t>
+          <t>391985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417551</t>
+          <t>416340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317043</t>
+          <t>316244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337908</t>
+          <t>337511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715112</t>
+          <t>714326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748754</t>
+          <t>747743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114979</t>
+          <t>114686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52613</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163046</t>
+          <t>162701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552782</t>
+          <t>553075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642212</t>
+          <t>641614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>114264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133141</t>
+          <t>133374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671625</t>
+          <t>671970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788905</t>
+          <t>792476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157952</t>
+          <t>156522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207465</t>
+          <t>204691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73026</t>
+          <t>69703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174446</t>
+          <t>173308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218770</t>
+          <t>231340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360850</t>
+          <t>361273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>826783</t>
+          <t>829557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876296</t>
+          <t>877726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>803107</t>
+          <t>804245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>904527</t>
+          <t>907850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650951</t>
+          <t>1650528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1793031</t>
+          <t>1780461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>75374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108527</t>
+          <t>108388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156001</t>
+          <t>156770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240619</t>
+          <t>239203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251080</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>333980</t>
+          <t>333362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365428</t>
+          <t>365567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399868</t>
+          <t>398581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599650</t>
+          <t>601066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>684268</t>
+          <t>683499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980244</t>
+          <t>980862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1063144</t>
+          <t>1072139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171261</t>
+          <t>172961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212357</t>
+          <t>211737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>175162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>218051</t>
+          <t>219464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227594</t>
+          <t>225733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237723</t>
+          <t>237702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>549014</t>
+          <t>549634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590110</t>
+          <t>588410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>783827</t>
+          <t>782414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>827990</t>
+          <t>826716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>326760</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>486415</t>
+          <t>485761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>564575</t>
+          <t>563822</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>745315</t>
+          <t>752844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>969381</t>
+          <t>966414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1213108</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2887481</t>
+          <t>2888135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3047136</t>
+          <t>3041241</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2830835</t>
+          <t>2823306</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3011575</t>
+          <t>3012328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5736939</t>
+          <t>5735612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5980666</t>
+          <t>5983633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0901-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>28609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52063</t>
+          <t>52606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59390</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95654</t>
+          <t>94988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422329</t>
+          <t>422235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446651</t>
+          <t>446654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254617</t>
+          <t>254074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277419</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>684803</t>
+          <t>685469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>721067</t>
+          <t>717819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29443</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48877</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>42106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72837</t>
+          <t>71215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337491</t>
+          <t>337779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322988</t>
+          <t>321542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345943</t>
+          <t>345178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665962</t>
+          <t>667584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>696044</t>
+          <t>696693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67180</t>
+          <t>67013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>48881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>72949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107642</t>
+          <t>107573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475209</t>
+          <t>475376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500787</t>
+          <t>501277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117936</t>
+          <t>118901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140409</t>
+          <t>140952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602529</t>
+          <t>602598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636589</t>
+          <t>637222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116324</t>
+          <t>114796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157429</t>
+          <t>157079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86210</t>
+          <t>86959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125120</t>
+          <t>124422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212398</t>
+          <t>213727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270691</t>
+          <t>272161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080905</t>
+          <t>1081255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1122010</t>
+          <t>1123538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589165</t>
+          <t>589863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628075</t>
+          <t>627326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1681929</t>
+          <t>1680459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1740222</t>
+          <t>1738893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54091</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71957</t>
+          <t>72430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>108367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108885</t>
+          <t>109864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150848</t>
+          <t>151880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296464</t>
+          <t>296588</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320873</t>
+          <t>321182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460774</t>
+          <t>460385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496795</t>
+          <t>496322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>768459</t>
+          <t>767427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>810422</t>
+          <t>809443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>216257</t>
+          <t>217770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>270455</t>
+          <t>272180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226914</t>
+          <t>226980</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>285371</t>
+          <t>282802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>282009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293620</t>
+          <t>293563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>978305</t>
+          <t>976580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1032503</t>
+          <t>1030990</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261589</t>
+          <t>1264158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320046</t>
+          <t>1319980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>264980</t>
+          <t>264191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>331447</t>
+          <t>331914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>506665</t>
+          <t>508384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>597116</t>
+          <t>596241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799583</t>
+          <t>795151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>903060</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2938743</t>
+          <t>2938276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3005210</t>
+          <t>3005999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2781008</t>
+          <t>2781883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2871459</t>
+          <t>2869740</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5745254</t>
+          <t>5743824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5848731</t>
+          <t>5853163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50810</t>
+          <t>49370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79210</t>
+          <t>82151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399893</t>
+          <t>398695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419715</t>
+          <t>419497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263644</t>
+          <t>265084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288682</t>
+          <t>289086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672455</t>
+          <t>669514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702795</t>
+          <t>701700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36544</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65789</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>53803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72244</t>
+          <t>73030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>113026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353008</t>
+          <t>353462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382253</t>
+          <t>382625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284211</t>
+          <t>284208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309726</t>
+          <t>309620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646511</t>
+          <t>643782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684564</t>
+          <t>683778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71449</t>
+          <t>71853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109957</t>
+          <t>110288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119799</t>
+          <t>120936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166488</t>
+          <t>167341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519458</t>
+          <t>519127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557966</t>
+          <t>557562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>190859</t>
+          <t>193031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217762</t>
+          <t>218977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>723056</t>
+          <t>722203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>769745</t>
+          <t>768608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139587</t>
+          <t>139836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191402</t>
+          <t>189436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98270</t>
+          <t>100966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141173</t>
+          <t>140987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253755</t>
+          <t>248632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316220</t>
+          <t>316843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>967607</t>
+          <t>969573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019422</t>
+          <t>1019173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625484</t>
+          <t>625670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>668387</t>
+          <t>665691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1609447</t>
+          <t>1608824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1671912</t>
+          <t>1677035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>54805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>86322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188013</t>
+          <t>188399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239254</t>
+          <t>241447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256195</t>
+          <t>254764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315715</t>
+          <t>313600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>423142</t>
+          <t>424274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455496</t>
+          <t>455791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522268</t>
+          <t>520075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>573509</t>
+          <t>573123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956403</t>
+          <t>958518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1015923</t>
+          <t>1017354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>248216</t>
+          <t>245554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304685</t>
+          <t>304161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257429</t>
+          <t>254387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317623</t>
+          <t>315038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244173</t>
+          <t>245174</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259439</t>
+          <t>260073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>804666</t>
+          <t>805190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>861135</t>
+          <t>863797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1058610</t>
+          <t>1061195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1118804</t>
+          <t>1121846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>371585</t>
+          <t>372736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>453750</t>
+          <t>456293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>692183</t>
+          <t>689302</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>794443</t>
+          <t>787351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1086931</t>
+          <t>1084814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1208969</t>
+          <t>1222058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2968160</t>
+          <t>2965617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3050325</t>
+          <t>3049174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2755682</t>
+          <t>2762774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2857942</t>
+          <t>2860823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5763066</t>
+          <t>5749977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5885104</t>
+          <t>5887221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55477</t>
+          <t>56307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58298</t>
+          <t>57346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66713</t>
+          <t>68233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103427</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373615</t>
+          <t>372785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399364</t>
+          <t>399766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288757</t>
+          <t>289709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315830</t>
+          <t>315658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672720</t>
+          <t>671223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709434</t>
+          <t>707914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>36121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>52823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>85837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340317</t>
+          <t>341106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359332</t>
+          <t>360305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315998</t>
+          <t>314240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341139</t>
+          <t>341479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665056</t>
+          <t>663663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697794</t>
+          <t>696677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68138</t>
+          <t>67725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74637</t>
+          <t>74256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111198</t>
+          <t>109570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453776</t>
+          <t>454189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481605</t>
+          <t>482244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117924</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140095</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576838</t>
+          <t>578466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613399</t>
+          <t>613780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113202</t>
+          <t>114703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160396</t>
+          <t>158044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103466</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146541</t>
+          <t>148025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229405</t>
+          <t>230869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290066</t>
+          <t>291509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989242</t>
+          <t>991594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1036436</t>
+          <t>1034935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679335</t>
+          <t>677851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>722410</t>
+          <t>722738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1685448</t>
+          <t>1684005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1746109</t>
+          <t>1744645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>76103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108129</t>
+          <t>111483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157712</t>
+          <t>158760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207174</t>
+          <t>207608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246590</t>
+          <t>244294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306300</t>
+          <t>303008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>512577</t>
+          <t>509223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>547395</t>
+          <t>544603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531070</t>
+          <t>530636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>580532</t>
+          <t>579484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1052650</t>
+          <t>1055942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1112360</t>
+          <t>1114656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>225978</t>
+          <t>228831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>287449</t>
+          <t>287886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234457</t>
+          <t>234009</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295232</t>
+          <t>297294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269079</t>
+          <t>271432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283500</t>
+          <t>283602</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>794576</t>
+          <t>794139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>856047</t>
+          <t>853194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1073938</t>
+          <t>1071876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1134713</t>
+          <t>1135161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>317751</t>
+          <t>320494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>390451</t>
+          <t>390262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>639379</t>
+          <t>640466</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>737408</t>
+          <t>740016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>976425</t>
+          <t>979201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1102140</t>
+          <t>1112628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2995271</t>
+          <t>2995460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3067971</t>
+          <t>3065228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2794188</t>
+          <t>2791580</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2892217</t>
+          <t>2891130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5815178</t>
+          <t>5804690</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5940893</t>
+          <t>5938117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42142</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>64962</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>53547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99961</t>
+          <t>109342</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>92277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120012</t>
+          <t>128823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>463070</t>
+          <t>506238</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449189</t>
+          <t>492247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>474190</t>
+          <t>517184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>389648</t>
+          <t>423449</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377513</t>
+          <t>410562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400573</t>
+          <t>434864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>852718</t>
+          <t>929687</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>832667</t>
+          <t>910206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>867392</t>
+          <t>946752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>36957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60228</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54786</t>
+          <t>63172</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>51944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66336</t>
+          <t>75107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>101870</t>
+          <t>112539</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87050</t>
+          <t>96964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120467</t>
+          <t>132448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>405129</t>
+          <t>433846</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391985</t>
+          <t>418656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416340</t>
+          <t>446255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>327794</t>
+          <t>359971</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316244</t>
+          <t>348036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337511</t>
+          <t>371199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>732923</t>
+          <t>793816</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714326</t>
+          <t>773907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747743</t>
+          <t>809391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>71598</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114686</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52647</t>
+          <t>58050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109870</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>101746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162701</t>
+          <t>139001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>599887</t>
+          <t>399521</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553075</t>
+          <t>382458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641614</t>
+          <t>415515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124915</t>
+          <t>140802</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114264</t>
+          <t>129447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133374</t>
+          <t>150195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>724801</t>
+          <t>540323</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671970</t>
+          <t>519615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>792476</t>
+          <t>556870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>180644</t>
+          <t>196465</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156522</t>
+          <t>171509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204691</t>
+          <t>222961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>132522</t>
+          <t>150761</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69703</t>
+          <t>133171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173308</t>
+          <t>170902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>313166</t>
+          <t>347225</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231340</t>
+          <t>317642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361273</t>
+          <t>379323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>853604</t>
+          <t>934792</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>829557</t>
+          <t>908296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877726</t>
+          <t>959748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>845031</t>
+          <t>709871</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>804245</t>
+          <t>689730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>907850</t>
+          <t>727461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1698635</t>
+          <t>1644664</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650528</t>
+          <t>1612566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1780461</t>
+          <t>1674247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034248</t>
+          <t>1131257</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034248</t>
+          <t>1131257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034248</t>
+          <t>1131257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011801</t>
+          <t>1991889</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011801</t>
+          <t>1991889</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011801</t>
+          <t>1991889</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91350</t>
+          <t>99011</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75374</t>
+          <t>82975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108388</t>
+          <t>120198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>207300</t>
+          <t>224197</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156770</t>
+          <t>204069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239203</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>298650</t>
+          <t>323208</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>296646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>333362</t>
+          <t>350570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>382605</t>
+          <t>467849</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365567</t>
+          <t>446662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398581</t>
+          <t>483885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>632969</t>
+          <t>605543</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>601066</t>
+          <t>584594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683499</t>
+          <t>625671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1015574</t>
+          <t>1073392</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980862</t>
+          <t>1046030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1072139</t>
+          <t>1099954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,22 +10348,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>191132</t>
+          <t>208824</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>172961</t>
+          <t>188736</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>211737</t>
+          <t>230692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>197225</t>
+          <t>214764</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175162</t>
+          <t>192786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219464</t>
+          <t>237684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234415</t>
+          <t>231288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225733</t>
+          <t>224408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237702</t>
+          <t>234464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>570239</t>
+          <t>635457</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>549634</t>
+          <t>613589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588410</t>
+          <t>655545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>804653</t>
+          <t>866745</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>782414</t>
+          <t>843825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>826716</t>
+          <t>888723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>435187</t>
+          <t>466760</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332655</t>
+          <t>427002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>485761</t>
+          <t>508275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>685554</t>
+          <t>758611</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>563822</t>
+          <t>716117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>752844</t>
+          <t>800230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1120742</t>
+          <t>1225371</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>966414</t>
+          <t>1169560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1214435</t>
+          <t>1285823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2938709</t>
+          <t>2973533</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2888135</t>
+          <t>2932018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3041241</t>
+          <t>3013291</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2890596</t>
+          <t>2875093</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2823306</t>
+          <t>2833474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3012328</t>
+          <t>2917587</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5829305</t>
+          <t>5848626</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5735612</t>
+          <t>5788174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5983633</t>
+          <t>5904437</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373896</t>
+          <t>3440293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373896</t>
+          <t>3440293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373896</t>
+          <t>3440293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950047</t>
+          <t>7073997</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950047</t>
+          <t>7073997</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950047</t>
+          <t>7073997</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
